--- a/Example/plate_layout.xlsx
+++ b/Example/plate_layout.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc63618c99ed4523/R/Lush/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ID Research Lab\Luz Cuello\Phages\Manuscripts\PST_methods_comparison\ARLG_only\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{2195DAE2-36E4-8843-978A-0A8F745AD53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C788D5-F8E8-0449-85ED-0D678BDEF083}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DF1BAA-40F1-4F88-B052-30C7E0DA3CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17820" yWindow="-20340" windowWidth="27640" windowHeight="16680" xr2:uid="{2BB10354-E9B2-AA48-ADC2-8D254AE3F52F}"/>
+    <workbookView xWindow="-210" yWindow="690" windowWidth="28770" windowHeight="16260" xr2:uid="{2BB10354-E9B2-AA48-ADC2-8D254AE3F52F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
   <si>
     <t>A</t>
   </si>
@@ -65,64 +65,109 @@
     <t>H</t>
   </si>
   <si>
-    <t>Control1</t>
-  </si>
-  <si>
-    <t>FA1</t>
-  </si>
-  <si>
-    <t>FA2</t>
-  </si>
-  <si>
-    <t>FA3</t>
-  </si>
-  <si>
-    <t>FA4</t>
-  </si>
-  <si>
-    <t>FA5</t>
-  </si>
-  <si>
-    <t>FA6</t>
-  </si>
-  <si>
-    <t>FA7</t>
-  </si>
-  <si>
-    <t>FA8</t>
-  </si>
-  <si>
-    <t>AB1</t>
-  </si>
-  <si>
-    <t>AB2</t>
-  </si>
-  <si>
-    <t>AB3</t>
-  </si>
-  <si>
-    <t>CA1</t>
-  </si>
-  <si>
-    <t>CA2</t>
-  </si>
-  <si>
-    <t>CA3</t>
-  </si>
-  <si>
-    <t>DA1</t>
-  </si>
-  <si>
-    <t>DA2</t>
-  </si>
-  <si>
-    <t>DA3</t>
-  </si>
-  <si>
-    <t>Control2</t>
-  </si>
-  <si>
-    <t>luz</t>
+    <t>Bestiario:3415</t>
+  </si>
+  <si>
+    <t>Cronopio:3415</t>
+  </si>
+  <si>
+    <t>Asterion:3415</t>
+  </si>
+  <si>
+    <t>3415 CTRL</t>
+  </si>
+  <si>
+    <t>Roth32:3415</t>
+  </si>
+  <si>
+    <t>Roth76:3415</t>
+  </si>
+  <si>
+    <t>Roth80:3415</t>
+  </si>
+  <si>
+    <t>Cronopio:4501</t>
+  </si>
+  <si>
+    <t>Asterion:4501</t>
+  </si>
+  <si>
+    <t>Roth32:4501</t>
+  </si>
+  <si>
+    <t>Roth76:4501</t>
+  </si>
+  <si>
+    <t>Roth80:4501</t>
+  </si>
+  <si>
+    <t>Bestiario:4653</t>
+  </si>
+  <si>
+    <t>Cronopio:4653</t>
+  </si>
+  <si>
+    <t>Asterion:4653</t>
+  </si>
+  <si>
+    <t>Roth32:4653</t>
+  </si>
+  <si>
+    <t>Roth76:4653</t>
+  </si>
+  <si>
+    <t>Roth80:4653</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Bestiario CTRL</t>
+  </si>
+  <si>
+    <t>Cronopio CTRL</t>
+  </si>
+  <si>
+    <t>Asterion CTRL</t>
+  </si>
+  <si>
+    <t>Roth32 CTRL</t>
+  </si>
+  <si>
+    <t>Roth76 CTRL</t>
+  </si>
+  <si>
+    <t>Roth80 CTRL</t>
+  </si>
+  <si>
+    <t>3415 e6</t>
+  </si>
+  <si>
+    <t>4501 e6</t>
+  </si>
+  <si>
+    <t>4653 e6</t>
+  </si>
+  <si>
+    <t>3415 e7</t>
+  </si>
+  <si>
+    <t>4501 e7</t>
+  </si>
+  <si>
+    <t>4653 e7</t>
+  </si>
+  <si>
+    <t>Bestiario:4501</t>
+  </si>
+  <si>
+    <t>4653 CTRL e5</t>
+  </si>
+  <si>
+    <t>3415 CTRL e5</t>
+  </si>
+  <si>
+    <t>4501 CTRL e5</t>
   </si>
 </sst>
 </file>
@@ -515,11 +560,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B6852B-5BA7-5440-9F95-B7ECA05B117F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC209E57-9DD3-4C09-8ED2-598F1B916ABA}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>1</v>
@@ -558,18 +613,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -590,225 +645,283 @@
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
